--- a/public_administration_forms/014_renewable_energy_policy_survey--public_administration_forms.xlsx
+++ b/public_administration_forms/014_renewable_energy_policy_survey--public_administration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,92 +515,100 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>form_first_page</t>
+          <t>current_status</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>form_first_page</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>What is the current status of renewable energy policy in your country/region?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please choose one of the options</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>form_page_two</t>
+          <t>energy_sources</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>form_page_two</t>
+          <t>Which renewable energy sources are currently being utilized in your country/region?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>form_policy_areas</t>
+          <t>challenges</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>policy_areas</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>What are the main challenges facing the implementation of renewable energy policies in your country/region?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Please provide a brief description</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>form_policy_areas_other</t>
+          <t>government_support</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>form_policy_areas_other</t>
+          <t>How does the government support the development of renewable energy technologies?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,18 +620,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>form_first_question</t>
+          <t>benefits</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>first_question</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>What are the main benefits of renewable energy policies in your country/region?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Please provide a brief description</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,87 +647,91 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>first_question_answer</t>
+          <t>solutions</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>first_question_answer</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>What are some potential solutions to the challenges facing renewable energy policies?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Please provide a brief description</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>form_second_question</t>
+          <t>public_perception</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>second_question</t>
+          <t>How does the public perceive renewable energy policies in your country/region?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>second_question_answer</t>
+          <t>media_promotion</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>second_question_answer</t>
+          <t>What role does the media play in promoting renewable energy policies?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>form_third_question</t>
+          <t>laws_and_regulations</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>third_question</t>
+          <t>Are there any specific laws or regulations that support or hinder renewable energy policies?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -727,361 +743,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>third_question_answer</t>
+          <t>additional_comments</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>third_question_answer</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Can you provide any additional comments or suggestions on the current state of renewable energy policies?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Please provide a brief description</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>form_policy_comments</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>policy_comments</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>form_policy_comments</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>policy_comments</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>form_last_question</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>last_question</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>last_question_answer</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>last_question_answer</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>form_policy_areas_other_text</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>policy_areas_other_text</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>form_other_solutions</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>other_solutions</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>other_solutions</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>other_solutions</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>form_other_comments</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>other_comments</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>other_comments</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>other_comments</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>form_policy_areas_other</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>policy_areas</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>form_other_solutions</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>other_solutions</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>form_other_solutions_2</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>other_solutions_2</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>form_other_comments_2</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>other_comments_2</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>other_comments_2</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>other_comments_2</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>form_last_submission</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>last_submission</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +773,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,204 +801,442 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>form_policy_areas_choices</t>
+          <t>current_status_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'name':_'solar',_'label':_'solar'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'name': 'solar', 'label': 'Solar'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>form_policy_areas_choices</t>
+          <t>current_status_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'name':_'wind',_'label':_'wind'}</t>
+          <t>implemented</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'name': 'wind', 'label': 'Wind'}</t>
+          <t>Implemented</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>form_policy_areas_choices</t>
+          <t>current_status_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'name':_'other',_'label':_'other'}</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'name': 'other', 'label': 'Other'}</t>
+          <t>Not Applicable</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>form_policy_areas_other_choices</t>
+          <t>current_status_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'name':_'solar',_'label':_'solar'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'name': 'solar', 'label': 'Solar'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>form_policy_areas_other_choices</t>
+          <t>energy_sources_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'name':_'wind',_'label':_'wind'}</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'name': 'wind', 'label': 'Wind'}</t>
+          <t>Solar</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>form_policy_areas_other_choices</t>
+          <t>energy_sources_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'name':_'other',_'label':_'other'}</t>
+          <t>wind</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'name': 'other', 'label': 'Other'}</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>form_other_solutions_choices</t>
+          <t>energy_sources_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'name':_'solution1',_'label':_'solution_1'}</t>
+          <t>hydro</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'name': 'solution1', 'label': 'Solution 1'}</t>
+          <t>Hydro</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>form_other_solutions_choices</t>
+          <t>energy_sources_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'name':_'solution2',_'label':_'solution_2'}</t>
+          <t>geothermal</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'name': 'solution2', 'label': 'Solution 2'}</t>
+          <t>Geothermal</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>form_other_solutions_choices</t>
+          <t>energy_sources_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'name':_'solution3',_'label':_'solution_3'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'name': 'solution3', 'label': 'Solution 3'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>form_other_solutions_2_choices</t>
+          <t>government_support_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'name':_'solution1',_'label':_'solution_1'}</t>
+          <t>financial_support</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'name': 'solution1', 'label': 'Solution 1'}</t>
+          <t>Financial Support</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>form_other_solutions_2_choices</t>
+          <t>government_support_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'name':_'solution2',_'label':_'solution_2'}</t>
+          <t>regulatory_support</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'name': 'solution2', 'label': 'Solution 2'}</t>
+          <t>Regulatory Support</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>form_other_solutions_2_choices</t>
+          <t>government_support_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'name':_'solution3',_'label':_'solution_3'}</t>
+          <t>technical_support</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'name': 'solution3', 'label': 'Solution 3'}</t>
+          <t>Technical Support</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>government_support_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>other_(please_specify)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Other (please specify)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>government_support_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>not_sufficient</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Not Sufficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>public_perception_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>public_perception_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>public_perception_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>public_perception_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>other_(please_specify)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Other (please specify)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>media_promotion_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>active_support</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Active Support</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>media_promotion_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>passive_support</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Passive Support</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>media_promotion_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>no_support</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>No Support</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>media_promotion_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>other_(please_specify)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Other (please specify)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>laws_and_regulations_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>supportive</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Supportive</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>laws_and_regulations_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>hindrance</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Hindrance</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>laws_and_regulations_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>laws_and_regulations_choices</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>other_(please_specify)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
